--- a/REPORT.xlsx
+++ b/REPORT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalyanchowdary.y\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDE16E1-E472-44A2-B7DD-1FE4A3C9755F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE30108-C46D-4A55-96E7-AEF7DE15DE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A24189A1-8977-4ACA-9854-53415AF02256}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
   <si>
     <t>Zone</t>
   </si>
@@ -62,69 +62,18 @@
     <t>Dilsuknagar</t>
   </si>
   <si>
-    <t>MANSOORABAD</t>
-  </si>
-  <si>
-    <t>Kalyan</t>
-  </si>
-  <si>
-    <t>cms person not came - Accountant leave</t>
-  </si>
-  <si>
-    <t>Vanasthalipuram</t>
-  </si>
-  <si>
-    <t>cms person not came</t>
-  </si>
-  <si>
     <t>Anantapur</t>
   </si>
   <si>
-    <t>ANANTHAPUR 10</t>
-  </si>
-  <si>
-    <t>Lakshmi G</t>
-  </si>
-  <si>
-    <t>after bank time coll</t>
-  </si>
-  <si>
-    <t>Rajahmundry</t>
-  </si>
-  <si>
-    <t>Sakhinetipalli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAI </t>
-  </si>
-  <si>
-    <t>Deposited but daysheet not closed due to receipts issue</t>
-  </si>
-  <si>
     <t>Howrah</t>
   </si>
   <si>
-    <t>SERAMPORE</t>
-  </si>
-  <si>
     <t>Rahamathulla</t>
   </si>
   <si>
-    <t>After bank time collection</t>
-  </si>
-  <si>
     <t>Visakhapatnam</t>
   </si>
   <si>
-    <t>KURMANNAPALEM</t>
-  </si>
-  <si>
-    <t>Ranjith</t>
-  </si>
-  <si>
-    <t>Deposit Done Due To Receipt Issue Daysheet Not Closed</t>
-  </si>
-  <si>
     <t>OPENING BALANCE</t>
   </si>
   <si>
@@ -179,9 +128,6 @@
     <t>Madhya Pradesh</t>
   </si>
   <si>
-    <t>Narayanguda</t>
-  </si>
-  <si>
     <t>Nellore</t>
   </si>
   <si>
@@ -194,9 +140,6 @@
     <t>CHHATTISGARH</t>
   </si>
   <si>
-    <t>Odisha</t>
-  </si>
-  <si>
     <t>Ongole</t>
   </si>
   <si>
@@ -207,6 +150,63 @@
   </si>
   <si>
     <t>AMOUNT</t>
+  </si>
+  <si>
+    <t>KURNOOL 11</t>
+  </si>
+  <si>
+    <t>Navaneeth Krishna</t>
+  </si>
+  <si>
+    <t>Bank Server Problem</t>
+  </si>
+  <si>
+    <t>NIZAMPET</t>
+  </si>
+  <si>
+    <t>Obulaiah</t>
+  </si>
+  <si>
+    <t>CMS person went to campus Accountant is not available</t>
+  </si>
+  <si>
+    <t>PU College NEW TOWN</t>
+  </si>
+  <si>
+    <t>Due to heavy rain</t>
+  </si>
+  <si>
+    <t>Poonamallee International School</t>
+  </si>
+  <si>
+    <t>Durga V T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">small amount </t>
+  </si>
+  <si>
+    <t>DHURI</t>
+  </si>
+  <si>
+    <t>Lavanya A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shortage amount 41150 </t>
+  </si>
+  <si>
+    <t>DHURI 2</t>
+  </si>
+  <si>
+    <t>shortage amount 305688</t>
+  </si>
+  <si>
+    <t>Ameerpet</t>
+  </si>
+  <si>
+    <t>Rajasthan</t>
+  </si>
+  <si>
+    <t>Gujarat</t>
   </si>
 </sst>
 </file>
@@ -304,7 +304,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -320,6 +320,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -655,399 +656,407 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC522DA-F175-46E2-A16B-D7FC27C94FB2}">
-  <dimension ref="A2:F43"/>
+  <dimension ref="A2:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <v>5915361</v>
+      <c r="A3" s="7">
+        <v>13497744</v>
       </c>
       <c r="B3" s="6">
         <v>40</v>
       </c>
       <c r="C3" s="6">
-        <v>13497744</v>
-      </c>
-      <c r="D3" s="6">
-        <v>30937268</v>
+        <v>7944250</v>
+      </c>
+      <c r="D3" s="7">
+        <v>36662806</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4">
-        <v>818719</v>
+        <v>1445790</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B8" s="4">
-        <v>683938</v>
+        <v>632104</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" s="4">
-        <v>677905</v>
+        <v>527080</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="B10" s="4">
-        <v>645989</v>
+        <v>519739</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B11" s="4">
-        <v>605585</v>
+        <v>511754</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B12" s="4">
-        <v>569116</v>
+        <v>468205</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B13" s="4">
-        <v>566245</v>
+        <v>464674</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B14" s="4">
-        <v>545290</v>
+        <v>385650</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
-        <v>453200</v>
+        <v>347338</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B16" s="4">
-        <v>449560</v>
+        <v>335600</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B17" s="4">
-        <v>427500</v>
+        <v>291000</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B18" s="4">
-        <v>345011</v>
+        <v>280720</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>332660</v>
+        <v>279900</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B20" s="4">
-        <v>322000</v>
+        <v>272105</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B21" s="4">
-        <v>269000</v>
+        <v>242330</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B22" s="4">
-        <v>254700</v>
+        <v>192000</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B23" s="4">
-        <v>244750</v>
+        <v>182500</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B24" s="4">
-        <v>234750</v>
+        <v>129399</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B25" s="4">
-        <v>230500</v>
+        <v>84500</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="B26" s="4">
-        <v>132000</v>
+        <v>82050</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B27" s="4">
-        <v>80399</v>
+        <v>80700</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4">
-        <v>79000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="B29" s="4">
-        <v>52000</v>
+        <v>67800</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="B30" s="4">
-        <v>49000</v>
+        <v>23260</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B31" s="4">
-        <v>48000</v>
+        <v>22650</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="B32" s="4">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E37" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D38" s="3">
-        <v>49360</v>
+        <v>83000</v>
       </c>
       <c r="E38" s="3">
-        <v>174360</v>
+        <v>83000</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" s="3">
-        <v>3500</v>
+        <v>72000</v>
       </c>
       <c r="E39" s="3">
-        <v>3500</v>
+        <v>72000</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D40" s="3">
-        <v>4</v>
+        <v>300</v>
       </c>
       <c r="E40" s="3">
-        <v>15004</v>
+        <v>400</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="D41" s="3">
-        <v>11000</v>
+        <v>41150</v>
       </c>
       <c r="E41" s="3">
-        <v>11000</v>
+        <v>41150</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="D42" s="3">
-        <v>350</v>
+        <v>305688</v>
       </c>
       <c r="E42" s="3">
-        <v>45750</v>
+        <v>305688</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D43" s="3">
-        <v>20500</v>
-      </c>
-      <c r="E43" s="3">
-        <v>20500</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/REPORT.xlsx
+++ b/REPORT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalyanchowdary.y\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE30108-C46D-4A55-96E7-AEF7DE15DE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C0A050-50F0-493F-BAFE-5A42BE4B6F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A24189A1-8977-4ACA-9854-53415AF02256}"/>
   </bookViews>
@@ -683,16 +683,16 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
-        <v>13497744</v>
+        <v>0</v>
       </c>
       <c r="B3" s="6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C3" s="6">
-        <v>7944250</v>
+        <v>0</v>
       </c>
       <c r="D3" s="7">
-        <v>36662806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -919,7 +919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>0</v>
       </c>

--- a/REPORT.xlsx
+++ b/REPORT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalyanchowdary.y\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C0A050-50F0-493F-BAFE-5A42BE4B6F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4002846-1908-463E-8B69-777D2CA77D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A24189A1-8977-4ACA-9854-53415AF02256}"/>
   </bookViews>
@@ -682,17 +682,17 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>0</v>
+      <c r="A3" s="6">
+        <v>13497744</v>
       </c>
       <c r="B3" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C3" s="6">
-        <v>0</v>
+        <v>7944250</v>
       </c>
       <c r="D3" s="7">
-        <v>0</v>
+        <v>36662806</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">

--- a/REPORT.xlsx
+++ b/REPORT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalyanchowdary.y\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4002846-1908-463E-8B69-777D2CA77D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989D03AC-7DBA-4A3B-B328-D2839DFDF96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A24189A1-8977-4ACA-9854-53415AF02256}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Zone</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Howrah</t>
   </si>
   <si>
-    <t>Rahamathulla</t>
-  </si>
-  <si>
     <t>Visakhapatnam</t>
   </si>
   <si>
@@ -152,54 +149,6 @@
     <t>AMOUNT</t>
   </si>
   <si>
-    <t>KURNOOL 11</t>
-  </si>
-  <si>
-    <t>Navaneeth Krishna</t>
-  </si>
-  <si>
-    <t>Bank Server Problem</t>
-  </si>
-  <si>
-    <t>NIZAMPET</t>
-  </si>
-  <si>
-    <t>Obulaiah</t>
-  </si>
-  <si>
-    <t>CMS person went to campus Accountant is not available</t>
-  </si>
-  <si>
-    <t>PU College NEW TOWN</t>
-  </si>
-  <si>
-    <t>Due to heavy rain</t>
-  </si>
-  <si>
-    <t>Poonamallee International School</t>
-  </si>
-  <si>
-    <t>Durga V T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">small amount </t>
-  </si>
-  <si>
-    <t>DHURI</t>
-  </si>
-  <si>
-    <t>Lavanya A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shortage amount 41150 </t>
-  </si>
-  <si>
-    <t>DHURI 2</t>
-  </si>
-  <si>
-    <t>shortage amount 305688</t>
-  </si>
-  <si>
     <t>Ameerpet</t>
   </si>
   <si>
@@ -207,6 +156,9 @@
   </si>
   <si>
     <t>Gujarat</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
   </si>
 </sst>
 </file>
@@ -249,7 +201,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -260,6 +212,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -315,12 +273,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -656,408 +618,352 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC522DA-F175-46E2-A16B-D7FC27C94FB2}">
-  <dimension ref="A2:F42"/>
+  <dimension ref="A2:F44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="51.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>13497744</v>
-      </c>
-      <c r="B3" s="6">
+        <v>7893250</v>
+      </c>
+      <c r="B3" s="7">
         <v>40</v>
       </c>
       <c r="C3" s="6">
-        <v>7944250</v>
-      </c>
-      <c r="D3" s="7">
-        <v>36662806</v>
+        <v>15727566</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1356950</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2">
+        <v>2779290</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1566105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1166010</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1057580</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1032864</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="2">
+        <v>998886</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2">
+        <v>867924</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B14" s="2">
+        <v>828104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="2">
+        <v>704830</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="2">
+        <v>660954</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="2">
+        <v>647650</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="2">
+        <v>507020</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="2">
+        <v>450500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>347338</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="2">
+        <v>301300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>279900</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="2">
+        <v>262899</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="2">
+        <v>252600</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="4">
-        <v>1445790</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="4">
-        <v>632104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="4">
-        <v>527080</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="4">
-        <v>519739</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4">
-        <v>511754</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4">
-        <v>468205</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="4">
-        <v>464674</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="4">
-        <v>385650</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="4">
-        <v>347338</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="4">
-        <v>335600</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="4">
-        <v>291000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="4">
-        <v>280720</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="4">
-        <v>279900</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="4">
-        <v>272105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="4">
-        <v>242330</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="B25" s="2">
+        <v>234950</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="2">
+        <v>215000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="4">
-        <v>192000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="B27" s="2">
+        <v>215000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="2">
+        <v>153000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="2">
+        <v>87650</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="2">
+        <v>86550</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>23260</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="4">
-        <v>182500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="4">
-        <v>129399</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="4">
-        <v>84500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="4">
-        <v>82050</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="4">
-        <v>80700</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="4">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="4">
-        <v>67800</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="4">
-        <v>23260</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" s="4">
-        <v>22650</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="4">
+      <c r="B32" s="2">
         <v>400</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" s="4">
+      <c r="A33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2">
+        <v>15727566</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="5"/>
+      <c r="B36" s="5"/>
+    </row>
+    <row r="38" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="3">
-        <v>8000</v>
-      </c>
-      <c r="E37" s="3">
-        <v>20000</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D38" s="3">
-        <v>83000</v>
-      </c>
-      <c r="E38" s="3">
-        <v>83000</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="3">
-        <v>72000</v>
-      </c>
-      <c r="E39" s="3">
-        <v>72000</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="2"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" s="3">
-        <v>300</v>
-      </c>
-      <c r="E40" s="3">
-        <v>400</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>47</v>
-      </c>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="2"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="3">
-        <v>41150</v>
-      </c>
-      <c r="E41" s="3">
-        <v>41150</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="2"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D42" s="3">
-        <v>305688</v>
-      </c>
-      <c r="E42" s="3">
-        <v>305688</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/REPORT.xlsx
+++ b/REPORT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalyanchowdary.y\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989D03AC-7DBA-4A3B-B328-D2839DFDF96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32E00BA-5779-45EA-9398-127C341DDB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A24189A1-8977-4ACA-9854-53415AF02256}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
   <si>
     <t>Zone</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>Grand Total</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -262,7 +265,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -276,7 +279,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -644,16 +646,16 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>7893250</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>40</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>15727566</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>1356950</v>
       </c>
     </row>
@@ -889,14 +891,6 @@
         <v>15727566</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-    </row>
     <row r="38" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>0</v>
@@ -918,12 +912,24 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="2"/>
+      <c r="A39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>

--- a/REPORT.xlsx
+++ b/REPORT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalyanchowdary.y\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32E00BA-5779-45EA-9398-127C341DDB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCE7775-571A-4518-BCC6-38D592AFEF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A24189A1-8977-4ACA-9854-53415AF02256}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
   <si>
     <t>Zone</t>
   </si>
@@ -156,9 +156,6 @@
   </si>
   <si>
     <t>Gujarat</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
   </si>
   <si>
     <t>-</t>
@@ -620,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC522DA-F175-46E2-A16B-D7FC27C94FB2}">
-  <dimension ref="A2:F44"/>
+  <dimension ref="A2:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -883,53 +880,53 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="2">
-        <v>15727566</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>5</v>
+      <c r="B38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="2"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
@@ -963,14 +960,6 @@
       <c r="E43" s="3"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
